--- a/astro-site/public/dl/kit-tareas/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas/01-apertura-cierre.xlsx
@@ -1,27 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Apertura Cocina" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Apertura Sala" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Apertura Barra" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cierre Cocina" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cierre Sala" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cierre Barra" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura Cocina" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura Sala" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura Barra" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Cocina" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Sala" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Barra" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Apertura Cocina'!$A$1:$G$45</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Apertura Sala'!$A$1:$G$41</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Apertura Barra'!$A$1:$G$32</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Cierre Cocina'!$A$1:$G$42</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Cierre Sala'!$A$1:$G$39</definedName>
-    <definedName localSheetId="6" name="_xlnm.Print_Area">'Cierre Barra'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura Cocina'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$45</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Apertura Sala'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Apertura Sala'!$A$1:$G$41</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Apertura Barra'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Apertura Barra'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Cierre Cocina'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cierre Cocina'!$A$1:$G$42</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Cierre Sala'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Cierre Sala'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Cierre Barra'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Cierre Barra'!$A$1:$G$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -159,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -181,78 +187,137 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="39">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="7" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="8" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="9" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="9" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -612,15 +677,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -628,6 +694,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -635,9 +702,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -673,9 +738,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -683,9 +746,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -714,9 +775,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr"/>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
@@ -724,8 +783,33 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -734,18 +818,18 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -762,10 +846,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -790,7 +875,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -805,18 +890,16 @@
           <t xml:space="preserve">  ENCENDIDO DE EQUIPOS</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="n"/>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="37" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="38" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -842,10 +925,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="38" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -871,10 +952,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="38" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -900,10 +979,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="38" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -929,10 +1006,8 @@
       <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="38" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -958,10 +1033,8 @@
       <c r="G10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="38" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -986,24 +1059,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="8" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  CONTROL DE TEMPERATURAS</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="37" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="38" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1029,10 +1101,8 @@
       <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="38" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1058,10 +1128,8 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="38" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1087,10 +1155,8 @@
       <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="38" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1115,24 +1181,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="8" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  REVISIÓN DE MERCANCÍA</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="37" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="38" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1158,10 +1223,8 @@
       <c r="G20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="38" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1187,10 +1250,8 @@
       <c r="G21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="38" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1216,10 +1277,8 @@
       <c r="G22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="38" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1244,24 +1303,23 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="8" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  MISE EN PLACE</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
+      <c r="B25" s="36" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="36" t="n"/>
+      <c r="G25" s="37" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="38" t="n">
+        <v>15</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -1287,10 +1345,8 @@
       <c r="G26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="38" t="n">
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -1316,10 +1372,8 @@
       <c r="G27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="38" t="n">
+        <v>17</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -1345,10 +1399,8 @@
       <c r="G28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="38" t="n">
+        <v>18</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -1374,10 +1426,8 @@
       <c r="G29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="38" t="n">
+        <v>19</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -1403,10 +1453,8 @@
       <c r="G30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A31" s="38" t="n">
+        <v>20</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -1432,10 +1480,8 @@
       <c r="G31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A32" s="38" t="n">
+        <v>21</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
@@ -1460,24 +1506,23 @@
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="8" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  LIMPIEZA PRE-SERVICIO</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
+      <c r="B34" s="36" t="n"/>
+      <c r="C34" s="36" t="n"/>
+      <c r="D34" s="36" t="n"/>
+      <c r="E34" s="36" t="n"/>
+      <c r="F34" s="36" t="n"/>
+      <c r="G34" s="37" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A35" s="38" t="n">
+        <v>22</v>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
@@ -1503,10 +1548,8 @@
       <c r="G35" s="8" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A36" s="38" t="n">
+        <v>23</v>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
@@ -1532,10 +1575,8 @@
       <c r="G36" s="8" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A37" s="38" t="n">
+        <v>24</v>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
@@ -1561,10 +1602,8 @@
       <c r="G37" s="8" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A38" s="38" t="n">
+        <v>25</v>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
@@ -1589,6 +1628,8 @@
       <c r="F38" s="14" t="n"/>
       <c r="G38" s="8" t="n"/>
     </row>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
@@ -1597,17 +1638,19 @@
       </c>
       <c r="D41" s="15">
         <f>COUNTIF(F5:F39,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F41" s="15" t="n">
-        <v>25</v>
-      </c>
-    </row>
+      <c r="F41" s="15">
+        <f>COUNTIF(B5:B39,"?*")</f>
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
@@ -1615,13 +1658,17 @@
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="37" t="n"/>
       <c r="E43" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F43" s="8" t="n"/>
-    </row>
+      <c r="G43" s="37" t="n"/>
+    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
         <is>
@@ -1633,8 +1680,8 @@
   <mergeCells count="10">
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B43:D43"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="B43:D43"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="A41:C41"/>
@@ -1642,13 +1689,26 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A19:G19"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G39">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F31 F32 F35 F36 F37 F38" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F31 F32 F35 F36 F37 F38 F39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1657,18 +1717,18 @@
   <sheetPr>
     <tabColor rgb="002196F3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1685,10 +1745,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1713,7 +1774,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1728,18 +1789,16 @@
           <t xml:space="preserve">  MONTAJE DE SALA</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="n"/>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="37" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="38" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1765,10 +1824,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="38" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1794,10 +1851,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="38" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1823,10 +1878,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="38" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1852,10 +1905,8 @@
       <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="38" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1881,10 +1932,8 @@
       <c r="G10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="38" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -1910,10 +1959,8 @@
       <c r="G11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="38" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -1938,24 +1985,23 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="8" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  MONTAJE DE TERRAZA</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
-      <c r="G14" s="22" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="37" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="38" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1981,10 +2027,8 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="38" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2010,10 +2054,8 @@
       <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="38" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2039,10 +2081,8 @@
       <c r="G17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="38" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -2068,10 +2108,8 @@
       <c r="G18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="38" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -2096,24 +2134,23 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="8" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  RESERVAS Y BRIEFING</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
-      <c r="G21" s="19" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="37" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="38" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -2139,10 +2176,8 @@
       <c r="G22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="38" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2168,10 +2203,8 @@
       <c r="G23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="38" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -2197,10 +2230,8 @@
       <c r="G24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="38" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -2226,10 +2257,8 @@
       <c r="G25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="38" t="n">
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -2255,10 +2284,8 @@
       <c r="G26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="38" t="n">
+        <v>18</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -2283,24 +2310,23 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="8" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  SISTEMAS</t>
         </is>
       </c>
-      <c r="B29" s="25" t="n"/>
-      <c r="C29" s="25" t="n"/>
-      <c r="D29" s="25" t="n"/>
-      <c r="E29" s="25" t="n"/>
-      <c r="F29" s="25" t="n"/>
-      <c r="G29" s="25" t="n"/>
+      <c r="B29" s="36" t="n"/>
+      <c r="C29" s="36" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="36" t="n"/>
+      <c r="F29" s="36" t="n"/>
+      <c r="G29" s="37" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="38" t="n">
+        <v>19</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -2326,10 +2352,8 @@
       <c r="G30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A31" s="38" t="n">
+        <v>20</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -2355,10 +2379,8 @@
       <c r="G31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A32" s="38" t="n">
+        <v>21</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
@@ -2384,10 +2406,8 @@
       <c r="G32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A33" s="38" t="n">
+        <v>22</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -2413,10 +2433,8 @@
       <c r="G33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A34" s="38" t="n">
+        <v>23</v>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
@@ -2441,6 +2459,8 @@
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="8" t="n"/>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
@@ -2449,17 +2469,19 @@
       </c>
       <c r="D37" s="15">
         <f>COUNTIF(F5:F35,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F37" s="15" t="n">
-        <v>23</v>
-      </c>
-    </row>
+      <c r="F37" s="15">
+        <f>COUNTIF(B5:B35,"?*")</f>
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
@@ -2467,13 +2489,17 @@
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
+      <c r="C39" s="36" t="n"/>
+      <c r="D39" s="37" t="n"/>
       <c r="E39" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F39" s="8" t="n"/>
-    </row>
+      <c r="G39" s="37" t="n"/>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
@@ -2493,13 +2519,26 @@
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="B39:D39"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G35">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F30 F31 F32 F33 F34" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2508,18 +2547,18 @@
   <sheetPr>
     <tabColor rgb="00FF9800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2536,10 +2575,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2564,7 +2604,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2579,18 +2619,16 @@
           <t xml:space="preserve">  PREPARACIÓN DE BARRA</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n"/>
-      <c r="C5" s="28" t="n"/>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="28" t="n"/>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="28" t="n"/>
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="n"/>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="37" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="38" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -2616,10 +2654,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="38" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2645,10 +2681,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="38" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2674,10 +2708,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="38" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2703,10 +2735,8 @@
       <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="38" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -2732,10 +2762,8 @@
       <c r="G10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="38" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -2761,10 +2789,8 @@
       <c r="G11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="38" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -2789,24 +2815,23 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="8" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÁQUINA DE CAFÉ</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="28" t="n"/>
-      <c r="E14" s="28" t="n"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="28" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="37" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="38" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2832,10 +2857,8 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="38" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2861,10 +2884,8 @@
       <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="38" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2890,10 +2911,8 @@
       <c r="G17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="38" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -2919,10 +2938,8 @@
       <c r="G18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="38" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -2947,24 +2964,23 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="8" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  CRISTALERÍA Y UTENSILIOS</t>
         </is>
       </c>
-      <c r="B21" s="28" t="n"/>
-      <c r="C21" s="28" t="n"/>
-      <c r="D21" s="28" t="n"/>
-      <c r="E21" s="28" t="n"/>
-      <c r="F21" s="28" t="n"/>
-      <c r="G21" s="28" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="37" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="38" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -2990,10 +3006,8 @@
       <c r="G22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="38" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -3019,10 +3033,8 @@
       <c r="G23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="38" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -3048,10 +3060,8 @@
       <c r="G24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="38" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -3076,6 +3086,8 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="8" t="n"/>
     </row>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
@@ -3084,17 +3096,19 @@
       </c>
       <c r="D28" s="15">
         <f>COUNTIF(F5:F26,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F28" s="15" t="n">
-        <v>16</v>
-      </c>
-    </row>
+      <c r="F28" s="15">
+        <f>COUNTIF(B5:B26,"?*")</f>
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
@@ -3102,13 +3116,17 @@
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="37" t="n"/>
       <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F30" s="8" t="n"/>
-    </row>
+      <c r="G30" s="37" t="n"/>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
@@ -3120,20 +3138,33 @@
   <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A21:G21"/>
-    <mergeCell ref="F30:G30"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A28:C28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3142,18 +3173,18 @@
   <sheetPr>
     <tabColor rgb="00388E3C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3170,10 +3201,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3198,7 +3230,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -3213,18 +3245,16 @@
           <t xml:space="preserve">  CONSERVACIÓN DE PRODUCTO</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="n"/>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="37" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="38" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -3250,10 +3280,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="38" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -3279,10 +3307,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="38" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -3308,10 +3334,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="38" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -3337,10 +3361,8 @@
       <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="38" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -3366,10 +3388,8 @@
       <c r="G10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="38" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -3394,24 +3414,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="8" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  LIMPIEZA DE PARTIDAS</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="37" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="38" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -3437,10 +3456,8 @@
       <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="38" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -3466,10 +3483,8 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="38" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -3495,10 +3510,8 @@
       <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="38" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -3524,10 +3537,8 @@
       <c r="G17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="38" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -3553,10 +3564,8 @@
       <c r="G18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="38" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -3581,24 +3590,23 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="8" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  LIMPIEZA GENERAL</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n"/>
-      <c r="C21" s="31" t="n"/>
-      <c r="D21" s="31" t="n"/>
-      <c r="E21" s="31" t="n"/>
-      <c r="F21" s="31" t="n"/>
-      <c r="G21" s="31" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="37" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="38" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -3624,10 +3632,8 @@
       <c r="G22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="38" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -3653,10 +3659,8 @@
       <c r="G23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="38" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -3682,10 +3686,8 @@
       <c r="G24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="38" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -3711,10 +3713,8 @@
       <c r="G25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="38" t="n">
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -3740,10 +3740,8 @@
       <c r="G26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="38" t="n">
+        <v>18</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -3768,24 +3766,23 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="8" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  APAGADO DE EQUIPOS</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
+      <c r="B29" s="36" t="n"/>
+      <c r="C29" s="36" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="36" t="n"/>
+      <c r="F29" s="36" t="n"/>
+      <c r="G29" s="37" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="38" t="n">
+        <v>19</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -3811,10 +3808,8 @@
       <c r="G30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A31" s="38" t="n">
+        <v>20</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -3840,10 +3835,8 @@
       <c r="G31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A32" s="38" t="n">
+        <v>21</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
@@ -3869,10 +3862,8 @@
       <c r="G32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A33" s="38" t="n">
+        <v>22</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -3898,10 +3889,8 @@
       <c r="G33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A34" s="38" t="n">
+        <v>23</v>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
@@ -3927,10 +3916,8 @@
       <c r="G34" s="8" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A35" s="38" t="n">
+        <v>24</v>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
@@ -3955,6 +3942,8 @@
       <c r="F35" s="14" t="n"/>
       <c r="G35" s="8" t="n"/>
     </row>
+    <row r="36"/>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
@@ -3963,17 +3952,19 @@
       </c>
       <c r="D38" s="15">
         <f>COUNTIF(F5:F36,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F38" s="15" t="n">
-        <v>24</v>
-      </c>
-    </row>
+      <c r="F38" s="15">
+        <f>COUNTIF(B5:B36,"?*")</f>
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -3981,13 +3972,17 @@
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
+      <c r="C40" s="36" t="n"/>
+      <c r="D40" s="37" t="n"/>
       <c r="E40" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F40" s="8" t="n"/>
-    </row>
+      <c r="G40" s="37" t="n"/>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
         <is>
@@ -3999,21 +3994,34 @@
   <mergeCells count="9">
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G36">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F30 F31 F32 F33 F34 F35" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F30 F31 F32 F33 F34 F35 F36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4022,18 +4030,18 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4050,10 +4058,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -4078,7 +4087,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -4093,18 +4102,16 @@
           <t xml:space="preserve">  RECOGIDA DE SALA</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="n"/>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="37" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="38" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -4130,10 +4137,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="38" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -4159,10 +4164,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="38" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -4188,10 +4191,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="38" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -4217,10 +4218,8 @@
       <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="38" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -4246,10 +4245,8 @@
       <c r="G10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="38" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -4274,24 +4271,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="8" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECOGIDA DE TERRAZA</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
-      <c r="G13" s="22" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="37" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="38" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -4317,10 +4313,8 @@
       <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="38" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -4346,10 +4340,8 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="38" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -4375,10 +4367,8 @@
       <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="38" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -4403,24 +4393,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="8" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE DE CAJA</t>
         </is>
       </c>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="25" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="37" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="38" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -4446,10 +4435,8 @@
       <c r="G20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="38" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -4475,10 +4462,8 @@
       <c r="G21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="38" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -4504,10 +4489,8 @@
       <c r="G22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="38" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -4533,10 +4516,8 @@
       <c r="G23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="38" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -4562,10 +4543,8 @@
       <c r="G24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="38" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -4590,24 +4569,23 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="8" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE GENERAL</t>
         </is>
       </c>
-      <c r="B27" s="34" t="n"/>
-      <c r="C27" s="34" t="n"/>
-      <c r="D27" s="34" t="n"/>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="34" t="n"/>
-      <c r="G27" s="34" t="n"/>
+      <c r="B27" s="36" t="n"/>
+      <c r="C27" s="36" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="36" t="n"/>
+      <c r="F27" s="36" t="n"/>
+      <c r="G27" s="37" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="38" t="n">
+        <v>17</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -4633,10 +4611,8 @@
       <c r="G28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="38" t="n">
+        <v>18</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -4662,10 +4638,8 @@
       <c r="G29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="38" t="n">
+        <v>19</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -4691,10 +4665,8 @@
       <c r="G30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A31" s="38" t="n">
+        <v>20</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -4720,10 +4692,8 @@
       <c r="G31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A32" s="38" t="n">
+        <v>21</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
@@ -4748,6 +4718,8 @@
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="8" t="n"/>
     </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
@@ -4756,17 +4728,19 @@
       </c>
       <c r="D35" s="15">
         <f>COUNTIF(F5:F33,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F35" s="15" t="n">
-        <v>21</v>
-      </c>
-    </row>
+      <c r="F35" s="15">
+        <f>COUNTIF(B5:B33,"?*")</f>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
@@ -4774,13 +4748,17 @@
         </is>
       </c>
       <c r="B37" s="8" t="n"/>
+      <c r="C37" s="36" t="n"/>
+      <c r="D37" s="37" t="n"/>
       <c r="E37" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F37" s="8" t="n"/>
-    </row>
+      <c r="G37" s="37" t="n"/>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
         <is>
@@ -4793,20 +4771,33 @@
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A13:G13"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A13:G13"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G33">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F28 F29 F30 F31 F32" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F28 F29 F30 F31 F32 F33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4815,18 +4806,18 @@
   <sheetPr>
     <tabColor rgb="00E65100"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4843,10 +4834,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -4871,7 +4863,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -4886,18 +4878,16 @@
           <t xml:space="preserve">  LIMPIEZA DE BARRA</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n"/>
-      <c r="C5" s="28" t="n"/>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="28" t="n"/>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="28" t="n"/>
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="n"/>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="37" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="38" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -4923,10 +4913,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="38" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -4952,10 +4940,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="38" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -4981,10 +4967,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="38" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -5010,10 +4994,8 @@
       <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="38" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -5039,10 +5021,8 @@
       <c r="G10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="38" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -5067,24 +5047,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="8" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  STOCK Y CONSERVACIÓN</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n"/>
-      <c r="C13" s="28" t="n"/>
-      <c r="D13" s="28" t="n"/>
-      <c r="E13" s="28" t="n"/>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="28" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="37" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="38" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -5110,10 +5089,8 @@
       <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="38" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -5139,10 +5116,8 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="38" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -5168,10 +5143,8 @@
       <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="38" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -5197,10 +5170,8 @@
       <c r="G17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="38" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -5226,10 +5197,8 @@
       <c r="G18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="38" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -5254,6 +5223,8 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="8" t="n"/>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
@@ -5262,17 +5233,19 @@
       </c>
       <c r="D22" s="15">
         <f>COUNTIF(F5:F20,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F22" s="15" t="n">
-        <v>12</v>
-      </c>
-    </row>
+      <c r="F22" s="15">
+        <f>COUNTIF(B5:B20,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -5280,13 +5253,17 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="37" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F24" s="8" t="n"/>
-    </row>
+      <c r="G24" s="37" t="n"/>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
@@ -5304,12 +5281,25 @@
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas/01-apertura-cierre.xlsx
@@ -16,18 +16,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Barra" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura Cocina'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Apertura Sala'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Apertura Sala'!$A$1:$G$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Apertura Sala'!$A$1:$G$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Apertura Barra'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Apertura Barra'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Apertura Barra'!$A$1:$G$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Cierre Cocina'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cierre Cocina'!$A$1:$G$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cierre Cocina'!$A$1:$G$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Cierre Sala'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Cierre Sala'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Cierre Sala'!$A$1:$G$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Cierre Barra'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Cierre Barra'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Cierre Barra'!$A$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,8 +109,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -162,6 +177,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F5"/>
         <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -235,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -302,6 +327,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -679,123 +777,230 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>Tareas de Apertura y Cierre — Restaurante Casual</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>Cómo usar estas plantillas</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>▸ Imprime la hoja correspondiente al turno (apertura o cierre)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>▸ El responsable del turno reparte las tareas al equipo</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>▸ Cada persona marca ✓ cuando completa su tarea y firma</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+    <row r="9" ht="16" customHeight="1">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>▸ Al final del turno, el encargado verifica y firma al pie</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="3" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>▸ Archiva las hojas firmadas — demuestran control operativo</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Cómo personalizar</t>
         </is>
       </c>
     </row>
     <row r="13"/>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="B14" s="41" t="inlineStr">
         <is>
           <t>▸ Las celdas verdes son editables — cambia responsables y horarios</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>▸ Borra las tareas que no aplican a tu restaurante</t>
+    <row r="15" ht="16" customHeight="1">
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>▸ Ajusta las horas límite a tus horarios reales</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>▸ Añade tareas específicas de tu local en las filas vacías del final</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>▸ Ajusta las horas límite a tus horarios reales</t>
+      <c r="B16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="18"/>
-    <row r="19">
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes · AI Chef Pro · aichef.pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
         </is>
       </c>
     </row>
     <row r="22"/>
-    <row r="23">
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="B25" s="41" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="B31" s="41" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="40" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="B35" s="41" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="B39" s="41" t="inlineStr">
+        <is>
+          <t>▸ Estás en 01-apertura-cierre.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="40" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="35" customHeight="1">
+      <c r="B43" s="40" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="40" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="40" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -820,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -885,817 +1090,1052 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HIGIENE PERSONAL</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="n"/>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="43" t="n"/>
+      <c r="E5" s="43" t="n"/>
+      <c r="F5" s="43" t="n"/>
+      <c r="G5" s="44" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>Uniforme y calzado de trabajo limpios, delantal cambiado y pelo recogido (gorro o redecilla)</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="48" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E6" s="48" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="50" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="46" t="inlineStr">
+        <is>
+          <t>Sin anillos, reloj ni pulseras; uñas cortas, limpias y sin esmalte</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="48" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E7" s="48" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="50" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>Heridas y cortes cubiertos con apósito impermeable de color visible y guante encima</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="48" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E8" s="48" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="50" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="46" t="inlineStr">
+        <is>
+          <t>Lavado de manos al entrar y en cada cambio de tarea; lavamanos con jabón, papel y agua caliente</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="48" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E9" s="48" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="50" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="46" t="inlineStr">
+        <is>
+          <t>Declarar síntomas digestivos o respiratorios: quien los tenga no manipula alimentos</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="48" t="inlineStr">
+        <is>
+          <t>Jefe de Cocina</t>
+        </is>
+      </c>
+      <c r="E10" s="48" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="50" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="51" t="n"/>
+      <c r="B11" s="51" t="n"/>
+      <c r="C11" s="51" t="n"/>
+      <c r="D11" s="51" t="n"/>
+      <c r="E11" s="51" t="n"/>
+      <c r="F11" s="51" t="n"/>
+      <c r="G11" s="51" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  ENCENDIDO DE EQUIPOS</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="37" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Encender cámaras frigoríficas y verificar temperaturas</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="B12" s="43" t="n"/>
+      <c r="C12" s="43" t="n"/>
+      <c r="D12" s="43" t="n"/>
+      <c r="E12" s="43" t="n"/>
+      <c r="F12" s="43" t="n"/>
+      <c r="G12" s="44" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="46" t="inlineStr">
+        <is>
+          <t>Encender la campana extractora y ventilar la cocina ANTES de encender nada más</t>
+        </is>
+      </c>
+      <c r="C13" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D13" s="48" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E13" s="48" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="F13" s="49" t="n"/>
+      <c r="G13" s="50" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="46" t="inlineStr">
+        <is>
+          <t>Abrir la llave general de gas y comprobar que NO huele a gas; si huele, no enciendas nada, ventila y avisa al mantenedor</t>
+        </is>
+      </c>
+      <c r="C14" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D14" s="48" t="inlineStr">
+        <is>
+          <t>Cocinero apertura</t>
+        </is>
+      </c>
+      <c r="E14" s="48" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F14" s="49" t="n"/>
+      <c r="G14" s="50" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>Encender hornos y precalentar a temperatura de trabajo</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E15" s="48" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="50" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>Encender planchas, freidoras y salamandra</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C16" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E16" s="48" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Encender campana extractora</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="50" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>Encender lavavajillas y verificar nivel de producto</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
+        <is>
+          <t>Auxiliar cocina</t>
+        </is>
+      </c>
+      <c r="E17" s="48" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="50" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>Comprobar que las cámaras han funcionado toda la noche y registrar temperatura (refrigeración 0-4 °C / congelación ≤ −18 °C) — anota la lectura: ____ °C. Si hay desviación, no uses el género hasta valorarlo</t>
+        </is>
+      </c>
+      <c r="C18" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="48" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E18" s="48" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Verificar gas: llaves abiertas, sin fugas</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="50" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="51" t="n"/>
+      <c r="B19" s="51" t="n"/>
+      <c r="C19" s="51" t="n"/>
+      <c r="D19" s="51" t="n"/>
+      <c r="E19" s="51" t="n"/>
+      <c r="F19" s="51" t="n"/>
+      <c r="G19" s="51" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTROL DE TEMPERATURAS</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="43" t="n"/>
+      <c r="D20" s="43" t="n"/>
+      <c r="E20" s="43" t="n"/>
+      <c r="F20" s="43" t="n"/>
+      <c r="G20" s="44" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>Registrar temperatura cámara 1 (refrigeración 0-4 °C) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C21" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D21" s="48" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E21" s="48" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="38" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Encender lavavajillas y verificar nivel de producto</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="50" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="46" t="inlineStr">
+        <is>
+          <t>Registrar temperatura cámara 2 (refrigeración 0-4 °C) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C22" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
+        <is>
+          <t>Cocinero apertura</t>
+        </is>
+      </c>
+      <c r="E22" s="48" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="50" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>Registrar temperatura congelador (congelación ≤ −18 °C) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C23" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D23" s="48" t="inlineStr">
+        <is>
+          <t>Cocinero apertura</t>
+        </is>
+      </c>
+      <c r="E23" s="48" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="50" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="46" t="inlineStr">
+        <is>
+          <t>Si tienes el Pack APPCC, registra la lectura en su hoja de temperaturas; si no, anótala aquí mismo: ____ °C</t>
+        </is>
+      </c>
+      <c r="C24" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D24" s="48" t="inlineStr">
+        <is>
+          <t>Cocinero apertura</t>
+        </is>
+      </c>
+      <c r="E24" s="48" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="50" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="51" t="n"/>
+      <c r="B25" s="51" t="n"/>
+      <c r="C25" s="51" t="n"/>
+      <c r="D25" s="51" t="n"/>
+      <c r="E25" s="51" t="n"/>
+      <c r="F25" s="51" t="n"/>
+      <c r="G25" s="51" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  REVISIÓN DE MERCANCÍA</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="43" t="n"/>
+      <c r="D26" s="43" t="n"/>
+      <c r="E26" s="43" t="n"/>
+      <c r="F26" s="43" t="n"/>
+      <c r="G26" s="44" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="45" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>Revisar caducidades en cámaras (FIFO)</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D27" s="48" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E27" s="48" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F27" s="49" t="n"/>
+      <c r="G27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>Verificar stock de productos del día</t>
+        </is>
+      </c>
+      <c r="C28" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D28" s="48" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E28" s="48" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F28" s="49" t="n"/>
+      <c r="G28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="45" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="46" t="inlineStr">
+        <is>
+          <t>Preparar lista de pedidos urgentes</t>
+        </is>
+      </c>
+      <c r="C29" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D29" s="48" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E29" s="48" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F29" s="49" t="n"/>
+      <c r="G29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="46" t="inlineStr">
+        <is>
+          <t>Recibir e inspeccionar entregas de proveedores</t>
+        </is>
+      </c>
+      <c r="C30" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D30" s="48" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E30" s="48" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F30" s="49" t="n"/>
+      <c r="G30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="n"/>
+      <c r="B31" s="51" t="n"/>
+      <c r="C31" s="51" t="n"/>
+      <c r="D31" s="51" t="n"/>
+      <c r="E31" s="51" t="n"/>
+      <c r="F31" s="51" t="n"/>
+      <c r="G31" s="51" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MISE EN PLACE</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="n"/>
+      <c r="C32" s="43" t="n"/>
+      <c r="D32" s="43" t="n"/>
+      <c r="E32" s="43" t="n"/>
+      <c r="F32" s="43" t="n"/>
+      <c r="G32" s="44" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="B33" s="46" t="inlineStr">
+        <is>
+          <t>Preparar mise en place de partida calientes</t>
+        </is>
+      </c>
+      <c r="C33" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D33" s="48" t="inlineStr">
+        <is>
+          <t>Chef partida</t>
+        </is>
+      </c>
+      <c r="E33" s="48" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F33" s="49" t="n"/>
+      <c r="G33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="45" t="n">
+        <v>21</v>
+      </c>
+      <c r="B34" s="46" t="inlineStr">
+        <is>
+          <t>Preparar mise en place de partida fríos</t>
+        </is>
+      </c>
+      <c r="C34" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D34" s="48" t="inlineStr">
+        <is>
+          <t>Chef partida</t>
+        </is>
+      </c>
+      <c r="E34" s="48" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F34" s="49" t="n"/>
+      <c r="G34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="45" t="n">
+        <v>22</v>
+      </c>
+      <c r="B35" s="46" t="inlineStr">
+        <is>
+          <t>Preparar salsas base del día</t>
+        </is>
+      </c>
+      <c r="C35" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D35" s="48" t="inlineStr">
+        <is>
+          <t>Cocinero</t>
+        </is>
+      </c>
+      <c r="E35" s="48" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F35" s="49" t="n"/>
+      <c r="G35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="45" t="n">
+        <v>23</v>
+      </c>
+      <c r="B36" s="46" t="inlineStr">
+        <is>
+          <t>Cortar vegetales y guarniciones</t>
+        </is>
+      </c>
+      <c r="C36" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D36" s="48" t="inlineStr">
         <is>
           <t>Auxiliar cocina</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="8" t="n"/>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CONTROL DE TEMPERATURAS</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="37" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Registrar temperatura cámara 1 (refrigeración)</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="E36" s="48" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F36" s="49" t="n"/>
+      <c r="G36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="45" t="n">
+        <v>24</v>
+      </c>
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>Preparar postres del día</t>
+        </is>
+      </c>
+      <c r="C37" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Cocinero apertura</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Registrar temperatura cámara 2 (refrigeración)</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="D37" s="48" t="inlineStr">
+        <is>
+          <t>Pastelero/Cocinero</t>
+        </is>
+      </c>
+      <c r="E37" s="48" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F37" s="49" t="n"/>
+      <c r="G37" s="50" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="B38" s="46" t="inlineStr">
+        <is>
+          <t>Montar mesa caliente / baño maría</t>
+        </is>
+      </c>
+      <c r="C38" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Cocinero apertura</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Registrar temperatura congelador</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="D38" s="48" t="inlineStr">
+        <is>
+          <t>Cocinero</t>
+        </is>
+      </c>
+      <c r="E38" s="48" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F38" s="49" t="n"/>
+      <c r="G38" s="50" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="45" t="n">
+        <v>26</v>
+      </c>
+      <c r="B39" s="46" t="inlineStr">
+        <is>
+          <t>Probar platos del día y ajustar sazón</t>
+        </is>
+      </c>
+      <c r="C39" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Cocinero apertura</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Registrar en hoja de control de temperaturas APPCC</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="D39" s="48" t="inlineStr">
+        <is>
+          <t>Jefe de Cocina</t>
+        </is>
+      </c>
+      <c r="E39" s="48" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="F39" s="49" t="n"/>
+      <c r="G39" s="50" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="n"/>
+      <c r="B40" s="51" t="n"/>
+      <c r="C40" s="51" t="n"/>
+      <c r="D40" s="51" t="n"/>
+      <c r="E40" s="51" t="n"/>
+      <c r="F40" s="51" t="n"/>
+      <c r="G40" s="51" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LIMPIEZA PRE-SERVICIO</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="n"/>
+      <c r="C41" s="43" t="n"/>
+      <c r="D41" s="43" t="n"/>
+      <c r="E41" s="43" t="n"/>
+      <c r="F41" s="43" t="n"/>
+      <c r="G41" s="44" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="45" t="n">
+        <v>27</v>
+      </c>
+      <c r="B42" s="46" t="inlineStr">
+        <is>
+          <t>Limpiar superficies de trabajo</t>
+        </is>
+      </c>
+      <c r="C42" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Cocinero apertura</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="8" t="n"/>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REVISIÓN DE MERCANCÍA</t>
-        </is>
-      </c>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="37" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="38" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Revisar caducidades en cámaras (FIFO)</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="D42" s="48" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E42" s="48" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F42" s="49" t="n"/>
+      <c r="G42" s="50" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="45" t="n">
+        <v>28</v>
+      </c>
+      <c r="B43" s="46" t="inlineStr">
+        <is>
+          <t>Verificar tablas de corte limpias por color</t>
+        </is>
+      </c>
+      <c r="C43" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D43" s="48" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Verificar stock de productos del día</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="E43" s="48" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F43" s="49" t="n"/>
+      <c r="G43" s="50" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="45" t="n">
+        <v>29</v>
+      </c>
+      <c r="B44" s="46" t="inlineStr">
+        <is>
+          <t>Verificar trapos limpios disponibles</t>
+        </is>
+      </c>
+      <c r="C44" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Sous Chef</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="38" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Preparar lista de pedidos urgentes</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="D44" s="48" t="inlineStr">
+        <is>
+          <t>Auxiliar cocina</t>
+        </is>
+      </c>
+      <c r="E44" s="48" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F44" s="49" t="n"/>
+      <c r="G44" s="50" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="45" t="n">
+        <v>30</v>
+      </c>
+      <c r="B45" s="46" t="inlineStr">
+        <is>
+          <t>Gel desinfectante en dispensadores</t>
+        </is>
+      </c>
+      <c r="C45" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Sous Chef</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Recibir e inspeccionar entregas de proveedores</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Sous Chef</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="8" t="n"/>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  MISE EN PLACE</t>
-        </is>
-      </c>
-      <c r="B25" s="36" t="n"/>
-      <c r="C25" s="36" t="n"/>
-      <c r="D25" s="36" t="n"/>
-      <c r="E25" s="36" t="n"/>
-      <c r="F25" s="36" t="n"/>
-      <c r="G25" s="37" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Preparar mise en place de partida calientes</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>Chef partida</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="38" t="n">
-        <v>16</v>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Preparar mise en place de partida fríos</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Chef partida</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="38" t="n">
-        <v>17</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Preparar salsas base del día</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Cocinero</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="38" t="n">
-        <v>18</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Cortar vegetales y guarniciones</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D45" s="48" t="inlineStr">
         <is>
           <t>Auxiliar cocina</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="38" t="n">
-        <v>19</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Preparar postres del día</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero/Cocinero</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="38" t="n">
-        <v>20</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Montar mesa caliente / baño maría</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Cocinero</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E45" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="38" t="n">
-        <v>21</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Probar platos del día y ajustar sazón</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Jefe de Cocina</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="8" t="n"/>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  LIMPIEZA PRE-SERVICIO</t>
-        </is>
-      </c>
-      <c r="B34" s="36" t="n"/>
-      <c r="C34" s="36" t="n"/>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="37" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="38" t="n">
-        <v>22</v>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Limpiar superficies de trabajo</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>Todo el equipo</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="8" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="38" t="n">
-        <v>23</v>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Verificar tablas de corte limpias por color</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>Sous Chef</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="38" t="n">
-        <v>24</v>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Verificar trapos limpios disponibles</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>Auxiliar cocina</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="n"/>
-      <c r="G37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="38" t="n">
-        <v>25</v>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Gel desinfectante en dispensadores</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>Auxiliar cocina</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="n"/>
-      <c r="G38" s="8" t="n"/>
-    </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="F45" s="49" t="n"/>
+      <c r="G45" s="50" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="52" t="n"/>
+      <c r="B46" s="53" t="n"/>
+      <c r="C46" s="47" t="n"/>
+      <c r="D46" s="48" t="n"/>
+      <c r="E46" s="48" t="n"/>
+      <c r="F46" s="49" t="n"/>
+      <c r="G46" s="50" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="52" t="n"/>
+      <c r="B47" s="53" t="n"/>
+      <c r="C47" s="47" t="n"/>
+      <c r="D47" s="48" t="n"/>
+      <c r="E47" s="48" t="n"/>
+      <c r="F47" s="49" t="n"/>
+      <c r="G47" s="50" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="52" t="n"/>
+      <c r="B48" s="53" t="n"/>
+      <c r="C48" s="47" t="n"/>
+      <c r="D48" s="48" t="n"/>
+      <c r="E48" s="48" t="n"/>
+      <c r="F48" s="49" t="n"/>
+      <c r="G48" s="50" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="52" t="n"/>
+      <c r="B49" s="53" t="n"/>
+      <c r="C49" s="47" t="n"/>
+      <c r="D49" s="48" t="n"/>
+      <c r="E49" s="48" t="n"/>
+      <c r="F49" s="49" t="n"/>
+      <c r="G49" s="50" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="52" t="n"/>
+      <c r="B50" s="53" t="n"/>
+      <c r="C50" s="47" t="n"/>
+      <c r="D50" s="48" t="n"/>
+      <c r="E50" s="48" t="n"/>
+      <c r="F50" s="49" t="n"/>
+      <c r="G50" s="50" t="n"/>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D41" s="15">
-        <f>COUNTIF(F5:F39,"✓")</f>
+      <c r="D52" s="15">
+        <f>COUNTIFS(B5:B50,"?*",F5:F50,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F41" s="15">
-        <f>COUNTIF(B5:B39,"?*")</f>
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="F52" s="15">
+        <f>COUNTIF(B5:B50,"?*")-COUNTIF(F5:F50,"N/A")</f>
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B43" s="8" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="37" t="n"/>
-      <c r="E43" s="15" t="inlineStr">
+      <c r="B54" s="54" t="n"/>
+      <c r="C54" s="36" t="n"/>
+      <c r="D54" s="37" t="n"/>
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="37" t="n"/>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="F54" s="54" t="n"/>
+      <c r="G54" s="37" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="F43:G43"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="11">
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="F54:G54"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G39">
+  <conditionalFormatting sqref="A5:G50">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F31 F32 F35 F36 F37 F38 F39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F27 F28 F29 F30 F33 F34 F35 F36 F37 F38 F39 F42 F43 F44 F45 F46 F47 F48 F49 F50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1719,7 +2159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1784,748 +2224,687 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  MONTAJE DE SALA</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="37" t="n"/>
+      <c r="B5" s="43" t="n"/>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="43" t="n"/>
+      <c r="E5" s="43" t="n"/>
+      <c r="F5" s="43" t="n"/>
+      <c r="G5" s="44" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>Encender luces y climatización</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>Camarero apertura</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="48" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>Verificar limpieza general de sala</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t>Camarero apertura</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="48" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>Montar mesas: manteles/individuales, cubiertos, vasos, servilletas</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t>Camareros</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="50" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>Colocar menús/cartas en mesas o atril</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="50" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>Verificar flores/decoración de mesas</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="48" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="50" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="46" t="inlineStr">
         <is>
           <t>Preparar estación de servicio: cubiertos extra, servilletas, salsas</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="48" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="8" t="n"/>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="50" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="46" t="inlineStr">
         <is>
           <t>Verificar carta de alérgenos accesible</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="48" t="inlineStr">
         <is>
           <t>Jefe de Sala</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="8" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="50" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="51" t="n"/>
+      <c r="B13" s="51" t="n"/>
+      <c r="C13" s="51" t="n"/>
+      <c r="D13" s="51" t="n"/>
+      <c r="E13" s="51" t="n"/>
+      <c r="F13" s="51" t="n"/>
+      <c r="G13" s="51" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">  MONTAJE DE TERRAZA</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="37" t="n"/>
+      <c r="B14" s="43" t="n"/>
+      <c r="C14" s="43" t="n"/>
+      <c r="D14" s="43" t="n"/>
+      <c r="E14" s="43" t="n"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="44" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="n">
+      <c r="A15" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>Sacar mobiliario de terraza</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>Camareros</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="48" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="50" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="n">
+      <c r="A16" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>Limpiar mesas y sillas de terraza</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="47" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="48" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="50" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="n">
+      <c r="A17" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Montar sombrillas/toldos si aplica</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="48" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="8" t="n"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="50" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="n">
+      <c r="A18" s="45" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Verificar calefactores exteriores (invierno)</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>Verificar calefactores exteriores si la terraza opera en temporada fría</t>
+        </is>
+      </c>
+      <c r="C18" s="47" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="48" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="48" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="50" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="n">
+      <c r="A19" s="45" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>Colocar ceniceros y servilleteros</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="47" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="48" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="48" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="8" t="n"/>
-    </row>
-    <row r="20"/>
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="50" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="51" t="n"/>
+      <c r="B20" s="51" t="n"/>
+      <c r="C20" s="51" t="n"/>
+      <c r="D20" s="51" t="n"/>
+      <c r="E20" s="51" t="n"/>
+      <c r="F20" s="51" t="n"/>
+      <c r="G20" s="51" t="n"/>
+    </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  RESERVAS Y BRIEFING</t>
         </is>
       </c>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="37" t="n"/>
+      <c r="B21" s="43" t="n"/>
+      <c r="C21" s="43" t="n"/>
+      <c r="D21" s="43" t="n"/>
+      <c r="E21" s="43" t="n"/>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="44" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="n">
+      <c r="A22" s="45" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="46" t="inlineStr">
         <is>
           <t>Revisar libro de reservas del día</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>Jefe de Sala</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="48" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="8" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="50" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="n">
+      <c r="A23" s="45" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="46" t="inlineStr">
         <is>
           <t>Asignar mesas a reservas con nombre</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="48" t="inlineStr">
         <is>
           <t>Jefe de Sala</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="48" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="8" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="50" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="n">
+      <c r="A24" s="45" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="46" t="inlineStr">
         <is>
           <t>Verificar eventos especiales (cumpleaños, grupos)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="48" t="inlineStr">
         <is>
           <t>Jefe de Sala</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="48" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="8" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="50" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="n">
+      <c r="A25" s="45" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="46" t="inlineStr">
         <is>
           <t>Briefing pre-servicio con equipo de sala</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="48" t="inlineStr">
         <is>
           <t>Jefe de Sala</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="48" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="8" t="n"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="50" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="38" t="n">
+      <c r="A26" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="46" t="inlineStr">
         <is>
           <t>Comunicar platos del día y alérgenos al equipo</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="48" t="inlineStr">
         <is>
           <t>Jefe de Sala</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="48" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="8" t="n"/>
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="50" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="n">
+      <c r="A27" s="45" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="46" t="inlineStr">
         <is>
           <t>Comunicar VIPs y peticiones especiales</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C27" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="48" t="inlineStr">
         <is>
           <t>Jefe de Sala</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="48" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="8" t="n"/>
-    </row>
-    <row r="28"/>
+      <c r="F27" s="49" t="n"/>
+      <c r="G27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="51" t="n"/>
+      <c r="B28" s="51" t="n"/>
+      <c r="C28" s="51" t="n"/>
+      <c r="D28" s="51" t="n"/>
+      <c r="E28" s="51" t="n"/>
+      <c r="F28" s="51" t="n"/>
+      <c r="G28" s="51" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SISTEMAS</t>
-        </is>
-      </c>
-      <c r="B29" s="36" t="n"/>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="36" t="n"/>
-      <c r="G29" s="37" t="n"/>
+      <c r="A29" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SISTEMAS → ver 08-apertura-cierre-negocio.xlsx (TPV, datáfono y música del local) y 09-apertura-cierre-caja.xlsx (fondo de caja, cajón y rollo de ticket)</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="n"/>
+      <c r="C29" s="43" t="n"/>
+      <c r="D29" s="43" t="n"/>
+      <c r="E29" s="43" t="n"/>
+      <c r="F29" s="43" t="n"/>
+      <c r="G29" s="44" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="n">
-        <v>19</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Encender TPV / sistema de cobro</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Encargado</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="8" t="n"/>
+      <c r="A30" s="52" t="n"/>
+      <c r="B30" s="53" t="n"/>
+      <c r="C30" s="47" t="n"/>
+      <c r="D30" s="48" t="n"/>
+      <c r="E30" s="48" t="n"/>
+      <c r="F30" s="49" t="n"/>
+      <c r="G30" s="50" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="38" t="n">
-        <v>20</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Verificar rollo de papel en TPV e impresora</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Encargado</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="8" t="n"/>
+      <c r="A31" s="52" t="n"/>
+      <c r="B31" s="53" t="n"/>
+      <c r="C31" s="47" t="n"/>
+      <c r="D31" s="48" t="n"/>
+      <c r="E31" s="48" t="n"/>
+      <c r="F31" s="49" t="n"/>
+      <c r="G31" s="50" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="n">
-        <v>21</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Abrir caja con fondo de cambio</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Encargado</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="8" t="n"/>
+      <c r="A32" s="52" t="n"/>
+      <c r="B32" s="53" t="n"/>
+      <c r="C32" s="47" t="n"/>
+      <c r="D32" s="48" t="n"/>
+      <c r="E32" s="48" t="n"/>
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="50" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="n">
-        <v>22</v>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Verificar datáfono funciona</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Encargado</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="8" t="n"/>
+      <c r="A33" s="52" t="n"/>
+      <c r="B33" s="53" t="n"/>
+      <c r="C33" s="47" t="n"/>
+      <c r="D33" s="48" t="n"/>
+      <c r="E33" s="48" t="n"/>
+      <c r="F33" s="49" t="n"/>
+      <c r="G33" s="50" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="38" t="n">
-        <v>23</v>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Comprobar música ambiental</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>Camarero</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="8" t="n"/>
+      <c r="A34" s="52" t="n"/>
+      <c r="B34" s="53" t="n"/>
+      <c r="C34" s="47" t="n"/>
+      <c r="D34" s="48" t="n"/>
+      <c r="E34" s="48" t="n"/>
+      <c r="F34" s="49" t="n"/>
+      <c r="G34" s="50" t="n"/>
     </row>
     <row r="35"/>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D37" s="15">
-        <f>COUNTIF(F5:F35,"✓")</f>
+      <c r="D36" s="15">
+        <f>COUNTIFS(B5:B34,"?*",F5:F34,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F37" s="15">
-        <f>COUNTIF(B5:B35,"?*")</f>
-        <v>23.0</v>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="F36" s="15">
+        <f>COUNTIF(B5:B34,"?*")-COUNTIF(F5:F34,"N/A")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="37" t="n"/>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="B38" s="54" t="n"/>
+      <c r="C38" s="36" t="n"/>
+      <c r="D38" s="37" t="n"/>
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="37" t="n"/>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="F38" s="54" t="n"/>
+      <c r="G38" s="37" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="F38:G38"/>
     <mergeCell ref="A29:G29"/>
-    <mergeCell ref="B39:D39"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G35">
+  <conditionalFormatting sqref="A5:G34">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F28 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2549,7 +2928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2614,544 +2993,605 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  PREPARACIÓN DE BARRA</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="37" t="n"/>
+      <c r="B5" s="43" t="n"/>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="43" t="n"/>
+      <c r="E5" s="43" t="n"/>
+      <c r="F5" s="43" t="n"/>
+      <c r="G5" s="44" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>Limpiar barra y superficies</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="48" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>Verificar stock de bebidas (cervezas, vinos, licores)</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="48" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>Reponer neveras de barra</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="48" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="50" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>Preparar cubeta de hielo</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="48" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="50" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>Cortar garnish: limón, naranja, lima, aceitunas</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="50" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="46" t="inlineStr">
         <is>
           <t>Preparar zumos frescos del día</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="8" t="n"/>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="50" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="46" t="inlineStr">
         <is>
           <t>Verificar stock de refrescos y agua</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="8" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="50" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="51" t="n"/>
+      <c r="B13" s="51" t="n"/>
+      <c r="C13" s="51" t="n"/>
+      <c r="D13" s="51" t="n"/>
+      <c r="E13" s="51" t="n"/>
+      <c r="F13" s="51" t="n"/>
+      <c r="G13" s="51" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÁQUINA DE CAFÉ</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="37" t="n"/>
+      <c r="B14" s="43" t="n"/>
+      <c r="C14" s="43" t="n"/>
+      <c r="D14" s="43" t="n"/>
+      <c r="E14" s="43" t="n"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="44" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="n">
+      <c r="A15" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>Encender máquina de café y dejar calentar</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="48" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="50" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="n">
+      <c r="A16" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>Purgar grupo de café (2 cafés al vacío)</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr">
+      <c r="C16" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="48" t="inlineStr">
         <is>
           <t>10:45</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="50" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="n">
+      <c r="A17" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Verificar stock de leche (entera, desnatada, vegetal)</t>
         </is>
       </c>
-      <c r="C17" s="29" t="inlineStr">
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="48" t="inlineStr">
         <is>
           <t>10:45</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="8" t="n"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="50" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="n">
+      <c r="A18" s="45" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="46" t="inlineStr">
         <is>
           <t>Limpiar vaporizador de leche</t>
         </is>
       </c>
-      <c r="C18" s="29" t="inlineStr">
+      <c r="C18" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="48" t="inlineStr">
         <is>
           <t>10:45</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="50" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="n">
+      <c r="A19" s="45" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>Verificar stock de azúcar, sacarina, estevia</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="48" t="inlineStr">
         <is>
           <t>10:45</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="8" t="n"/>
-    </row>
-    <row r="20"/>
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="50" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="51" t="n"/>
+      <c r="B20" s="51" t="n"/>
+      <c r="C20" s="51" t="n"/>
+      <c r="D20" s="51" t="n"/>
+      <c r="E20" s="51" t="n"/>
+      <c r="F20" s="51" t="n"/>
+      <c r="G20" s="51" t="n"/>
+    </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  CRISTALERÍA Y UTENSILIOS</t>
         </is>
       </c>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="37" t="n"/>
+      <c r="B21" s="43" t="n"/>
+      <c r="C21" s="43" t="n"/>
+      <c r="D21" s="43" t="n"/>
+      <c r="E21" s="43" t="n"/>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="44" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="n">
+      <c r="A22" s="45" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="46" t="inlineStr">
         <is>
           <t>Verificar cristalería limpia y sin marcas</t>
         </is>
       </c>
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="8" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="50" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="n">
+      <c r="A23" s="45" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="46" t="inlineStr">
         <is>
           <t>Reponer posavasos y servilletas de barra</t>
         </is>
       </c>
-      <c r="C23" s="29" t="inlineStr">
+      <c r="C23" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="8" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="50" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="n">
+      <c r="A24" s="45" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="46" t="inlineStr">
         <is>
           <t>Verificar coctelera, jigger, colador, muddler</t>
         </is>
       </c>
-      <c r="C24" s="29" t="inlineStr">
+      <c r="C24" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="8" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="50" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="n">
+      <c r="A25" s="45" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="46" t="inlineStr">
         <is>
           <t>Verificar pajitas y removedores</t>
         </is>
       </c>
-      <c r="C25" s="29" t="inlineStr">
+      <c r="C25" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="48" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="8" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="50" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="52" t="n"/>
+      <c r="B26" s="53" t="n"/>
+      <c r="C26" s="47" t="n"/>
+      <c r="D26" s="48" t="n"/>
+      <c r="E26" s="48" t="n"/>
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="52" t="n"/>
+      <c r="B27" s="53" t="n"/>
+      <c r="C27" s="47" t="n"/>
+      <c r="D27" s="48" t="n"/>
+      <c r="E27" s="48" t="n"/>
+      <c r="F27" s="49" t="n"/>
+      <c r="G27" s="50" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D28" s="15">
-        <f>COUNTIF(F5:F26,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F28" s="15">
-        <f>COUNTIF(B5:B26,"?*")</f>
-        <v>16.0</v>
-      </c>
-    </row>
-    <row r="29"/>
+      <c r="A28" s="52" t="n"/>
+      <c r="B28" s="53" t="n"/>
+      <c r="C28" s="47" t="n"/>
+      <c r="D28" s="48" t="n"/>
+      <c r="E28" s="48" t="n"/>
+      <c r="F28" s="49" t="n"/>
+      <c r="G28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="52" t="n"/>
+      <c r="B29" s="53" t="n"/>
+      <c r="C29" s="47" t="n"/>
+      <c r="D29" s="48" t="n"/>
+      <c r="E29" s="48" t="n"/>
+      <c r="F29" s="49" t="n"/>
+      <c r="G29" s="50" t="n"/>
+    </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="37" t="n"/>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="37" t="n"/>
+      <c r="A30" s="52" t="n"/>
+      <c r="B30" s="53" t="n"/>
+      <c r="C30" s="47" t="n"/>
+      <c r="D30" s="48" t="n"/>
+      <c r="E30" s="48" t="n"/>
+      <c r="F30" s="49" t="n"/>
+      <c r="G30" s="50" t="n"/>
     </row>
     <row r="31"/>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D32" s="15">
+        <f>COUNTIFS(B5:B30,"?*",F5:F30,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F32" s="15">
+        <f>COUNTIF(B5:B30,"?*")-COUNTIF(F5:F30,"N/A")</f>
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B34" s="54" t="n"/>
+      <c r="C34" s="36" t="n"/>
+      <c r="D34" s="37" t="n"/>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F34" s="54" t="n"/>
+      <c r="G34" s="37" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="F34:G34"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A21:G21"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G26">
+  <conditionalFormatting sqref="A5:G30">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3175,7 +3615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3225,7 +3665,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -3240,775 +3680,871 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  CONSERVACIÓN DE PRODUCTO</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="37" t="n"/>
+      <c r="B5" s="43" t="n"/>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="43" t="n"/>
+      <c r="E5" s="43" t="n"/>
+      <c r="F5" s="43" t="n"/>
+      <c r="G5" s="44" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>Etiquetar y fechar todas las pre-elaboraciones</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>Cocineros</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>Guardar mise en place en recipientes herméticos</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t>Cocineros</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>Aplicar FIFO en cámaras: producto nuevo atrás</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t>Cocineros</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="50" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>Retirar producto caducado o deteriorado</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="50" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
+        <is>
+          <t>Anotar las mermas del día (producto, cantidad y motivo): sin este dato el food cost mensual sale mal</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="48" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E10" s="48" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="50" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="46" t="inlineStr">
         <is>
           <t>Cubrir todos los recipientes en cámaras</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D11" s="48" t="inlineStr">
         <is>
           <t>Cocineros</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E11" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="38" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Registrar temperatura final cámaras y congelador</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="50" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="46" t="inlineStr">
+        <is>
+          <t>Registrar temperatura final cámaras y congelador (refrigeración 0-4 °C / congelación ≤ −18 °C) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D12" s="48" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E12" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="8" t="n"/>
-    </row>
-    <row r="12"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="50" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="51" t="n"/>
+      <c r="B13" s="51" t="n"/>
+      <c r="C13" s="51" t="n"/>
+      <c r="D13" s="51" t="n"/>
+      <c r="E13" s="51" t="n"/>
+      <c r="F13" s="51" t="n"/>
+      <c r="G13" s="51" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  LIMPIEZA DE PARTIDAS</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="37" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="43" t="n"/>
+      <c r="C14" s="43" t="n"/>
+      <c r="D14" s="43" t="n"/>
+      <c r="E14" s="43" t="n"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="44" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>Limpiar y desinfectar superficies de trabajo</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>Todo el equipo</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E15" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="50" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>Limpiar plancha, fogones y freidora</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C16" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>Cocinero partida</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E16" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="50" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Limpiar horno y salamandra</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>Cocinero partida</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E17" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="50" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
         <is>
           <t>Vaciar y limpiar baño maría</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C18" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D18" s="48" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E18" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="38" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="50" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>Limpiar tablas de corte y cuchillos</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C19" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D19" s="48" t="inlineStr">
         <is>
           <t>Todo el equipo</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E19" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="50" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
         <is>
           <t>Lavar y guardar utensilios</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C20" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D20" s="48" t="inlineStr">
         <is>
           <t>Auxiliar cocina</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E20" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="8" t="n"/>
-    </row>
-    <row r="20"/>
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="50" t="n"/>
+    </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="51" t="n"/>
+      <c r="B21" s="51" t="n"/>
+      <c r="C21" s="51" t="n"/>
+      <c r="D21" s="51" t="n"/>
+      <c r="E21" s="51" t="n"/>
+      <c r="F21" s="51" t="n"/>
+      <c r="G21" s="51" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">  LIMPIEZA GENERAL</t>
         </is>
       </c>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="37" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="38" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="43" t="n"/>
+      <c r="C22" s="43" t="n"/>
+      <c r="D22" s="43" t="n"/>
+      <c r="E22" s="43" t="n"/>
+      <c r="F22" s="43" t="n"/>
+      <c r="G22" s="44" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="46" t="inlineStr">
         <is>
           <t>Barrer suelos de cocina</t>
         </is>
       </c>
-      <c r="C22" s="32" t="inlineStr">
+      <c r="C23" s="47" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D23" s="48" t="inlineStr">
         <is>
           <t>Auxiliar cocina</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E23" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="50" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="46" t="inlineStr">
         <is>
           <t>Fregar suelos de cocina</t>
         </is>
       </c>
-      <c r="C23" s="32" t="inlineStr">
+      <c r="C24" s="47" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D24" s="48" t="inlineStr">
         <is>
           <t>Auxiliar cocina</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E24" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="50" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="46" t="inlineStr">
         <is>
           <t>Vaciar cubos de basura y colocar bolsas nuevas</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C25" s="47" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D25" s="48" t="inlineStr">
         <is>
           <t>Auxiliar cocina</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E25" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="38" t="n">
-        <v>16</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="50" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="46" t="inlineStr">
         <is>
           <t>Sacar basura a contenedores</t>
         </is>
       </c>
-      <c r="C25" s="32" t="inlineStr">
+      <c r="C26" s="47" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D26" s="48" t="inlineStr">
         <is>
           <t>Auxiliar cocina</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E26" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="38" t="n">
-        <v>17</v>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="45" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" s="46" t="inlineStr">
         <is>
           <t>Limpiar fregaderos</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr">
+      <c r="C27" s="47" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D27" s="48" t="inlineStr">
         <is>
           <t>Auxiliar cocina</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E27" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="38" t="n">
-        <v>18</v>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="F27" s="49" t="n"/>
+      <c r="G27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
         <is>
           <t>Verificar trampas de grasa</t>
         </is>
       </c>
-      <c r="C27" s="32" t="inlineStr">
+      <c r="C28" s="47" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D28" s="48" t="inlineStr">
         <is>
           <t>Auxiliar cocina</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E28" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="8" t="n"/>
-    </row>
-    <row r="28"/>
+      <c r="F28" s="49" t="n"/>
+      <c r="G28" s="50" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="51" t="n"/>
+      <c r="B29" s="51" t="n"/>
+      <c r="C29" s="51" t="n"/>
+      <c r="D29" s="51" t="n"/>
+      <c r="E29" s="51" t="n"/>
+      <c r="F29" s="51" t="n"/>
+      <c r="G29" s="51" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  APAGADO DE EQUIPOS</t>
         </is>
       </c>
-      <c r="B29" s="36" t="n"/>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="36" t="n"/>
-      <c r="G29" s="37" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="38" t="n">
-        <v>19</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="43" t="n"/>
+      <c r="C30" s="43" t="n"/>
+      <c r="D30" s="43" t="n"/>
+      <c r="E30" s="43" t="n"/>
+      <c r="F30" s="43" t="n"/>
+      <c r="G30" s="44" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" s="46" t="inlineStr">
         <is>
           <t>Apagar freidoras y plancha</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C31" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D31" s="48" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E31" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="38" t="n">
-        <v>20</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="F31" s="49" t="n"/>
+      <c r="G31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="n">
+        <v>21</v>
+      </c>
+      <c r="B32" s="46" t="inlineStr">
         <is>
           <t>Apagar hornos y salamandra</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C32" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D32" s="48" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E32" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="38" t="n">
-        <v>21</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="45" t="n">
+        <v>22</v>
+      </c>
+      <c r="B33" s="46" t="inlineStr">
         <is>
           <t>Cerrar llaves de gas</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C33" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D33" s="48" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E33" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="38" t="n">
-        <v>22</v>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="F33" s="49" t="n"/>
+      <c r="G33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="45" t="n">
+        <v>23</v>
+      </c>
+      <c r="B34" s="46" t="inlineStr">
         <is>
           <t>Apagar campana extractora</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C34" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D34" s="48" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E34" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="38" t="n">
-        <v>23</v>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="F34" s="49" t="n"/>
+      <c r="G34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="45" t="n">
+        <v>24</v>
+      </c>
+      <c r="B35" s="46" t="inlineStr">
         <is>
           <t>Verificar que cámaras quedan cerradas</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C35" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D35" s="48" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E35" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="8" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="38" t="n">
-        <v>24</v>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="F35" s="49" t="n"/>
+      <c r="G35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="B36" s="46" t="inlineStr">
         <is>
           <t>Apagar luces de cocina</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C36" s="47" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D36" s="48" t="inlineStr">
         <is>
           <t>Último en salir</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="E36" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="8" t="n"/>
-    </row>
-    <row r="36"/>
-    <row r="37"/>
+      <c r="F36" s="49" t="n"/>
+      <c r="G36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="52" t="n"/>
+      <c r="B37" s="53" t="n"/>
+      <c r="C37" s="47" t="n"/>
+      <c r="D37" s="48" t="n"/>
+      <c r="E37" s="48" t="n"/>
+      <c r="F37" s="49" t="n"/>
+      <c r="G37" s="50" t="n"/>
+    </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="52" t="n"/>
+      <c r="B38" s="53" t="n"/>
+      <c r="C38" s="47" t="n"/>
+      <c r="D38" s="48" t="n"/>
+      <c r="E38" s="48" t="n"/>
+      <c r="F38" s="49" t="n"/>
+      <c r="G38" s="50" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="52" t="n"/>
+      <c r="B39" s="53" t="n"/>
+      <c r="C39" s="47" t="n"/>
+      <c r="D39" s="48" t="n"/>
+      <c r="E39" s="48" t="n"/>
+      <c r="F39" s="49" t="n"/>
+      <c r="G39" s="50" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="52" t="n"/>
+      <c r="B40" s="53" t="n"/>
+      <c r="C40" s="47" t="n"/>
+      <c r="D40" s="48" t="n"/>
+      <c r="E40" s="48" t="n"/>
+      <c r="F40" s="49" t="n"/>
+      <c r="G40" s="50" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="52" t="n"/>
+      <c r="B41" s="53" t="n"/>
+      <c r="C41" s="47" t="n"/>
+      <c r="D41" s="48" t="n"/>
+      <c r="E41" s="48" t="n"/>
+      <c r="F41" s="49" t="n"/>
+      <c r="G41" s="50" t="n"/>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D38" s="15">
-        <f>COUNTIF(F5:F36,"✓")</f>
+      <c r="D43" s="15">
+        <f>COUNTIFS(B5:B41,"?*",F5:F41,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E43" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F38" s="15">
-        <f>COUNTIF(B5:B36,"?*")</f>
-        <v>24.0</v>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="F43" s="15">
+        <f>COUNTIF(B5:B41,"?*")-COUNTIF(F5:F41,"N/A")</f>
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="36" t="n"/>
-      <c r="D40" s="37" t="n"/>
-      <c r="E40" s="15" t="inlineStr">
+      <c r="B45" s="54" t="n"/>
+      <c r="C45" s="36" t="n"/>
+      <c r="D45" s="37" t="n"/>
+      <c r="E45" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="37" t="n"/>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="F45" s="54" t="n"/>
+      <c r="G45" s="37" t="n"/>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="9">
-    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="F45:G45"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G36">
+  <conditionalFormatting sqref="A5:G41">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F30 F31 F32 F33 F34 F35 F36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4032,7 +4568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4082,7 +4618,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -4097,694 +4633,477 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECOGIDA DE SALA</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="37" t="n"/>
+      <c r="B5" s="43" t="n"/>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="43" t="n"/>
+      <c r="E5" s="43" t="n"/>
+      <c r="F5" s="43" t="n"/>
+      <c r="G5" s="44" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>Desmontar mesas: recoger manteles, cubiertos, vasos</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>Camareros</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>Limpiar y desinfectar mesas</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t>Camareros</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>Recoger estación de servicio</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="50" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>Reponer servilletas, cubiertos y salsas para mañana</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="50" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>Barrer y fregar suelos de sala</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="48" t="inlineStr">
         <is>
           <t>Personal limpieza</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="50" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="46" t="inlineStr">
         <is>
           <t>Verificar baños: limpieza, jabón, papel</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="48" t="inlineStr">
         <is>
           <t>Personal limpieza</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="8" t="n"/>
-    </row>
-    <row r="12"/>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="50" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="51" t="n"/>
+      <c r="B12" s="51" t="n"/>
+      <c r="C12" s="51" t="n"/>
+      <c r="D12" s="51" t="n"/>
+      <c r="E12" s="51" t="n"/>
+      <c r="F12" s="51" t="n"/>
+      <c r="G12" s="51" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">  RECOGIDA DE TERRAZA</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="37" t="n"/>
+      <c r="B13" s="43" t="n"/>
+      <c r="C13" s="43" t="n"/>
+      <c r="D13" s="43" t="n"/>
+      <c r="E13" s="43" t="n"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="44" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="n">
+      <c r="A14" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>Recoger mesas y sillas de terraza</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="47" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="48" t="inlineStr">
         <is>
           <t>Camareros</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="F14" s="49" t="n"/>
+      <c r="G14" s="50" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="n">
+      <c r="A15" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>Recoger sombrillas/toldos</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="50" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="n">
+      <c r="A16" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>Barrer terraza</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="47" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="50" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="n">
+      <c r="A17" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Guardar mobiliario si es necesario</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="8" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="50" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="51" t="n"/>
+      <c r="B18" s="51" t="n"/>
+      <c r="C18" s="51" t="n"/>
+      <c r="D18" s="51" t="n"/>
+      <c r="E18" s="51" t="n"/>
+      <c r="F18" s="51" t="n"/>
+      <c r="G18" s="51" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CIERRE DE CAJA</t>
-        </is>
-      </c>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="37" t="n"/>
+      <c r="A19" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CIERRE DE CAJA → ver 09-apertura-cierre-caja.xlsx: fondo, recuento por denominaciones, Z del TPV y descuadre</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="n"/>
+      <c r="C19" s="43" t="n"/>
+      <c r="D19" s="43" t="n"/>
+      <c r="E19" s="43" t="n"/>
+      <c r="F19" s="43" t="n"/>
+      <c r="G19" s="44" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Imprimir informe Z del TPV</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Encargado</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>Cierre</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="8" t="n"/>
+      <c r="A20" s="51" t="n"/>
+      <c r="B20" s="51" t="n"/>
+      <c r="C20" s="51" t="n"/>
+      <c r="D20" s="51" t="n"/>
+      <c r="E20" s="51" t="n"/>
+      <c r="F20" s="51" t="n"/>
+      <c r="G20" s="51" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Contar efectivo y cuadrar con TPV</t>
-        </is>
-      </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Encargado</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>Cierre</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="8" t="n"/>
+      <c r="A21" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CIERRE GENERAL → ver 08-apertura-cierre-negocio.xlsx: alarma, luces, climatización, cierre y llaves</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="n"/>
+      <c r="C21" s="43" t="n"/>
+      <c r="D21" s="43" t="n"/>
+      <c r="E21" s="43" t="n"/>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="44" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Registrar propinas si aplica</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Encargado</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Cierre</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="8" t="n"/>
+      <c r="A22" s="52" t="n"/>
+      <c r="B22" s="53" t="n"/>
+      <c r="C22" s="47" t="n"/>
+      <c r="D22" s="48" t="n"/>
+      <c r="E22" s="48" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="50" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Guardar efectivo en caja fuerte</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Encargado</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>Cierre</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="8" t="n"/>
+      <c r="A23" s="52" t="n"/>
+      <c r="B23" s="53" t="n"/>
+      <c r="C23" s="47" t="n"/>
+      <c r="D23" s="48" t="n"/>
+      <c r="E23" s="48" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="50" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Apagar TPV y datáfono</t>
-        </is>
-      </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Encargado</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>Cierre</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="8" t="n"/>
+      <c r="A24" s="52" t="n"/>
+      <c r="B24" s="53" t="n"/>
+      <c r="C24" s="47" t="n"/>
+      <c r="D24" s="48" t="n"/>
+      <c r="E24" s="48" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="50" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="n">
-        <v>16</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Registrar incidencias del turno</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Encargado</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>Cierre</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="8" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CIERRE GENERAL</t>
-        </is>
-      </c>
-      <c r="B27" s="36" t="n"/>
-      <c r="C27" s="36" t="n"/>
-      <c r="D27" s="36" t="n"/>
-      <c r="E27" s="36" t="n"/>
-      <c r="F27" s="36" t="n"/>
-      <c r="G27" s="37" t="n"/>
-    </row>
+      <c r="A25" s="52" t="n"/>
+      <c r="B25" s="53" t="n"/>
+      <c r="C25" s="47" t="n"/>
+      <c r="D25" s="48" t="n"/>
+      <c r="E25" s="48" t="n"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="50" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="52" t="n"/>
+      <c r="B26" s="53" t="n"/>
+      <c r="C26" s="47" t="n"/>
+      <c r="D26" s="48" t="n"/>
+      <c r="E26" s="48" t="n"/>
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="50" t="n"/>
+    </row>
+    <row r="27"/>
     <row r="28">
-      <c r="A28" s="38" t="n">
-        <v>17</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Apagar música y TV</t>
-        </is>
-      </c>
-      <c r="C28" s="35" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Último en salir</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>Cierre</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="38" t="n">
-        <v>18</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Apagar climatización</t>
-        </is>
-      </c>
-      <c r="C29" s="35" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Último en salir</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>Cierre</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="8" t="n"/>
-    </row>
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D28" s="15">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F28" s="15">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
-      <c r="A30" s="38" t="n">
-        <v>19</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Verificar ventanas cerradas</t>
-        </is>
-      </c>
-      <c r="C30" s="35" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Último en salir</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>Cierre</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="38" t="n">
-        <v>20</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Activar alarma</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Último en salir</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>Cierre</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="8" t="n"/>
-    </row>
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B30" s="54" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="37" t="n"/>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F30" s="54" t="n"/>
+      <c r="G30" s="37" t="n"/>
+    </row>
+    <row r="31"/>
     <row r="32">
-      <c r="A32" s="38" t="n">
-        <v>21</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Cerrar puerta con llave</t>
-        </is>
-      </c>
-      <c r="C32" s="35" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Último en salir</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>Cierre</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="8" t="n"/>
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
     </row>
     <row r="33"/>
     <row r="34"/>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D35" s="15">
-        <f>COUNTIF(F5:F33,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F35" s="15">
-        <f>COUNTIF(B5:B33,"?*")</f>
-        <v>21.0</v>
-      </c>
-    </row>
+    <row r="35"/>
     <row r="36"/>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="36" t="n"/>
-      <c r="D37" s="37" t="n"/>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="37" t="n"/>
-    </row>
+    <row r="37"/>
     <row r="38"/>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
-        </is>
-      </c>
-    </row>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="9">
-    <mergeCell ref="F37:G37"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G33">
+  <conditionalFormatting sqref="A5:G26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F28 F29 F30 F31 F32 F33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F20 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4808,7 +5127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4858,7 +5177,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -4873,421 +5192,474 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  LIMPIEZA DE BARRA</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="37" t="n"/>
+      <c r="B5" s="43" t="n"/>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="43" t="n"/>
+      <c r="E5" s="43" t="n"/>
+      <c r="F5" s="43" t="n"/>
+      <c r="G5" s="44" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>Limpiar y desinfectar superficie de barra</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>Limpiar máquina de café: purgar, limpiar grupo</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>Limpiar vaporizador de leche</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="50" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>Lavar y guardar cristalería</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="50" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>Lavar coctelera, jigger y utensilios</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="50" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="46" t="inlineStr">
         <is>
           <t>Limpiar fregadero de barra</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="8" t="n"/>
-    </row>
-    <row r="12"/>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="50" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="51" t="n"/>
+      <c r="B12" s="51" t="n"/>
+      <c r="C12" s="51" t="n"/>
+      <c r="D12" s="51" t="n"/>
+      <c r="E12" s="51" t="n"/>
+      <c r="F12" s="51" t="n"/>
+      <c r="G12" s="51" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  STOCK Y CONSERVACIÓN</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="37" t="n"/>
+      <c r="B13" s="43" t="n"/>
+      <c r="C13" s="43" t="n"/>
+      <c r="D13" s="43" t="n"/>
+      <c r="E13" s="43" t="n"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="44" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="n">
+      <c r="A14" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>Guardar garnish sobrante en recipientes</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="F14" s="49" t="n"/>
+      <c r="G14" s="50" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="n">
+      <c r="A15" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>Verificar stock de cerveza (barriles, botellas)</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="50" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="n">
+      <c r="A16" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>Cerrar neveras de barra</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr">
+      <c r="C16" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="50" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="n">
+      <c r="A17" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Desechar hielo sobrante y limpiar cubeta</t>
         </is>
       </c>
-      <c r="C17" s="29" t="inlineStr">
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="8" t="n"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="50" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="n">
+      <c r="A18" s="45" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="46" t="inlineStr">
         <is>
           <t>Anotar productos a pedir para mañana</t>
         </is>
       </c>
-      <c r="C18" s="29" t="inlineStr">
+      <c r="C18" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="50" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="n">
+      <c r="A19" s="45" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>Apagar máquina de café</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" s="47" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="48" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="48" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="8" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="50" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="52" t="n"/>
+      <c r="B20" s="53" t="n"/>
+      <c r="C20" s="47" t="n"/>
+      <c r="D20" s="48" t="n"/>
+      <c r="E20" s="48" t="n"/>
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="50" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="52" t="n"/>
+      <c r="B21" s="53" t="n"/>
+      <c r="C21" s="47" t="n"/>
+      <c r="D21" s="48" t="n"/>
+      <c r="E21" s="48" t="n"/>
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="50" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D22" s="15">
-        <f>COUNTIF(F5:F20,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F22" s="15">
-        <f>COUNTIF(B5:B20,"?*")</f>
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="23"/>
+      <c r="A22" s="52" t="n"/>
+      <c r="B22" s="53" t="n"/>
+      <c r="C22" s="47" t="n"/>
+      <c r="D22" s="48" t="n"/>
+      <c r="E22" s="48" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="50" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="52" t="n"/>
+      <c r="B23" s="53" t="n"/>
+      <c r="C23" s="47" t="n"/>
+      <c r="D23" s="48" t="n"/>
+      <c r="E23" s="48" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="50" t="n"/>
+    </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="37" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="37" t="n"/>
+      <c r="A24" s="52" t="n"/>
+      <c r="B24" s="53" t="n"/>
+      <c r="C24" s="47" t="n"/>
+      <c r="D24" s="48" t="n"/>
+      <c r="E24" s="48" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="50" t="n"/>
     </row>
     <row r="25"/>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D26" s="15">
+        <f>COUNTIFS(B5:B24,"?*",F5:F24,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F26" s="15">
+        <f>COUNTIF(B5:B24,"?*")-COUNTIF(F5:F24,"N/A")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B28" s="54" t="n"/>
+      <c r="C28" s="36" t="n"/>
+      <c r="D28" s="37" t="n"/>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F28" s="54" t="n"/>
+      <c r="G28" s="37" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F28:G28"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="B28:D28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G20">
+  <conditionalFormatting sqref="A5:G24">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/astro-site/public/dl/kit-tareas/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas/01-apertura-cierre.xlsx
@@ -899,6 +899,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="32" customHeight="1">
       <c r="B25" s="41" t="inlineStr">
         <is>
@@ -913,6 +914,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="40" t="inlineStr">
         <is>
@@ -920,6 +922,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="32" customHeight="1">
       <c r="B30" s="41" t="inlineStr">
         <is>
@@ -934,6 +937,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="40" t="inlineStr">
         <is>
@@ -941,10 +945,11 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="32" customHeight="1">
+    <row r="34"/>
+    <row r="35" ht="16" customHeight="1">
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
         </is>
       </c>
     </row>
@@ -962,10 +967,10 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
+    <row r="38" ht="48" customHeight="1">
       <c r="B38" s="41" t="inlineStr">
         <is>
-          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
         </is>
       </c>
     </row>
@@ -976,6 +981,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="40" t="inlineStr">
         <is>
@@ -983,6 +989,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43" ht="35" customHeight="1">
       <c r="B43" s="40" t="inlineStr">
         <is>
@@ -997,6 +1004,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="40" t="inlineStr">
         <is>
@@ -2135,7 +2143,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F27 F28 F29 F30 F33 F34 F35 F36 F37 F38 F39 F42 F43 F44 F45 F46 F47 F48 F49 F50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F27 F28 F29 F30 F33 F34 F35 F36 F37 F38 F39 F42 F43 F44 F45 F46 F47 F48 F49 F50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2159,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2880,11 +2888,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="9">
@@ -2894,9 +2897,9 @@
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="F38:G38"/>
-    <mergeCell ref="A29:G29"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G34">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -2904,7 +2907,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F28 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F28 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3578,9 +3581,9 @@
   <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F34:G34"/>
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A21:G21"/>
@@ -3591,7 +3594,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4531,11 +4534,11 @@
     <mergeCell ref="F45:G45"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B45:D45"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A43:C43"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G41">
@@ -4544,7 +4547,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4568,7 +4571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5073,17 +5076,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="9">
@@ -5103,7 +5095,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F20 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F20 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5659,7 +5651,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
